--- a/legacy/nola_2024_results.xlsx
+++ b/legacy/nola_2024_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="1-Seed Draw" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,6 +25,76 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="I26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Changed to 8 from 6, based on other player scores</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Changed to 62 from 60, based on corrected round 4 score</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Changed to 5 from 10, based on other player scores</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Changed to 50 from 51 (presumed value used for Pts Pct computation), unclearly written</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Changed to 42 from 47, based on corrected round 7 score</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
@@ -65,7 +135,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Changed to 8 from 2, to make consistent with PF4 column (average of discrepancy)</t>
+          <t xml:space="preserve">Changed to 5 from 2, to make consistent with PF4 column (average of the discrepancy)</t>
         </r>
       </text>
     </comment>
@@ -969,23 +1039,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC9211E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -3781,7 +3834,7 @@
         <v>8</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O26" s="6" t="n">
         <v>6</v>
@@ -3812,7 +3865,7 @@
       </c>
       <c r="X26" s="7" t="n">
         <f aca="false">N26/(N26+W26)</f>
-        <v>0.461538461538462</v>
+        <v>0.46969696969697</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4276,11 +4329,11 @@
         <v>10</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="X32" s="7" t="n">
         <f aca="false">N32/(N32+W32)</f>
-        <v>0.591304347826087</v>
+        <v>0.618181818181818</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4447,6 +4500,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/legacy/nola_2024_results.xlsx
+++ b/legacy/nola_2024_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1-Seed Draw" sheetId="1" state="visible" r:id="rId3"/>
@@ -985,7 +985,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1024,6 +1024,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2069,7 +2073,7 @@
       <c r="W3" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="X3" s="7" t="n">
+      <c r="X3" s="10" t="n">
         <f aca="false">N3/(N3+W3)</f>
         <v>0.545454545454545</v>
       </c>
@@ -3863,7 +3867,7 @@
       <c r="W26" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="X26" s="7" t="n">
+      <c r="X26" s="10" t="n">
         <f aca="false">N26/(N26+W26)</f>
         <v>0.46969696969697</v>
       </c>
@@ -4331,7 +4335,7 @@
       <c r="W32" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="X32" s="7" t="n">
+      <c r="X32" s="10" t="n">
         <f aca="false">N32/(N32+W32)</f>
         <v>0.618181818181818</v>
       </c>
@@ -6872,8 +6876,8 @@
       <c r="M12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="N12" s="6" t="n">
-        <v>68</v>
+      <c r="N12" s="9" t="n">
+        <v>71</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>10</v>
@@ -6904,7 +6908,7 @@
       </c>
       <c r="X12" s="7" t="n">
         <f aca="false">N12/(N12+W12)</f>
-        <v>0.519083969465649</v>
+        <v>0.529850746268657</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7028,8 +7032,8 @@
       <c r="M14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="N14" s="6" t="n">
-        <v>58</v>
+      <c r="N14" s="9" t="n">
+        <v>54</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>10</v>
@@ -7060,7 +7064,7 @@
       </c>
       <c r="X14" s="7" t="n">
         <f aca="false">N14/(N14+W14)</f>
-        <v>0.456692913385827</v>
+        <v>0.439024390243902</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7211,12 +7215,12 @@
       <c r="V16" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="W16" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="X16" s="7" t="n">
+      <c r="W16" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="X16" s="10" t="n">
         <f aca="false">N16/(N16+W16)</f>
-        <v>0.436507936507937</v>
+        <v>0.447154471544715</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7686,7 +7690,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="24.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="5" width="12.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="11.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="10" width="10.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="10.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7737,7 +7741,7 @@
       <c r="G2" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="11" t="n">
         <v>0.563</v>
       </c>
     </row>
@@ -7763,7 +7767,7 @@
       <c r="G3" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="H3" s="10" t="n">
+      <c r="H3" s="11" t="n">
         <v>0.489</v>
       </c>
     </row>
@@ -7789,7 +7793,7 @@
       <c r="G4" s="5" t="n">
         <v>0.333</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="11" t="n">
         <v>0.472</v>
       </c>
     </row>
@@ -7815,7 +7819,7 @@
       <c r="G5" s="5" t="n">
         <v>0.333</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="11" t="n">
         <v>0.444</v>
       </c>
     </row>

--- a/legacy/nola_2024_results.xlsx
+++ b/legacy/nola_2024_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="1-Seed Draw" sheetId="1" state="visible" r:id="rId3"/>
@@ -5020,9 +5020,14 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="18.11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.77"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="24.77"/>
   </cols>
   <sheetData>
@@ -7322,7 +7327,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="24.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="23.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="6" width="7.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="8.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="6" width="5.46"/>
